--- a/tools/importer/reports/import-cuztomgraft-landing-page.report.xlsx
+++ b/tools/importer/reports/import-cuztomgraft-landing-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>en-gb.report.json</t>
   </si>
   <si>
-    <t>["hero","form"]</t>
+    <t>["form","hero"]</t>
   </si>
   <si>
     <t>en-gb</t>
@@ -52,7 +52,7 @@
     <t>cuztomgraft-landing-page</t>
   </si>
   <si>
-    <t>2026-05-07T10:51:06.495Z</t>
+    <t>2026-05-07T11:06:37.974Z</t>
   </si>
   <si>
     <t>ZimVie Dental Upload-Form</t>
